--- a/data/processed/recettes_mensuelles.xlsx
+++ b/data/processed/recettes_mensuelles.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,19 +473,64 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>lag_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>lag_3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lag_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>moyenne_mobile</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rolling_6</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_rolling_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_diff</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>trend</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -495,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="D2" t="n">
         <v>100715</v>
@@ -504,14 +549,29 @@
         <v>792</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8660254037844387</v>
+      </c>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -521,7 +581,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="D3" t="n">
         <v>105322</v>
@@ -530,16 +590,35 @@
         <v>713</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="J3" t="n">
         <v>100715</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>792</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>-79</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -549,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="D4" t="n">
         <v>114985</v>
@@ -558,17 +637,34 @@
         <v>715</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="J4" t="n">
         <v>105322</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>107007.3333333333</v>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>713</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -579,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="D5" t="n">
         <v>84472</v>
@@ -588,19 +684,42 @@
         <v>588</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="J5" t="n">
         <v>114985</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>100715</v>
       </c>
-      <c r="J5" t="n">
-        <v>101593</v>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>107007.3333333333</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>715</v>
+      </c>
+      <c r="P5" t="n">
+        <v>792</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>740</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-127</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -611,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="D6" t="n">
         <v>108284</v>
@@ -620,19 +739,42 @@
         <v>716</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="J6" t="n">
         <v>84472</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>105322</v>
       </c>
-      <c r="J6" t="n">
-        <v>102580.3333333333</v>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>101593</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>588</v>
+      </c>
+      <c r="P6" t="n">
+        <v>713</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>672</v>
+      </c>
+      <c r="R6" t="n">
+        <v>128</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -643,7 +785,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="D7" t="n">
         <v>79788</v>
@@ -652,19 +794,42 @@
         <v>504</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" t="n">
         <v>108284</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>114985</v>
       </c>
-      <c r="J7" t="n">
-        <v>90848</v>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>102580.3333333333</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>716</v>
+      </c>
+      <c r="P7" t="n">
+        <v>715</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-212</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -675,7 +840,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="D8" t="n">
         <v>64345</v>
@@ -684,19 +849,46 @@
         <v>345</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="J8" t="n">
         <v>79788</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>84472</v>
       </c>
-      <c r="J8" t="n">
-        <v>84139</v>
+      <c r="L8" t="n">
+        <v>100715</v>
+      </c>
+      <c r="M8" t="n">
+        <v>90848</v>
+      </c>
+      <c r="N8" t="n">
+        <v>98927.66666666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>504</v>
+      </c>
+      <c r="P8" t="n">
+        <v>588</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>602.6666666666666</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-159</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="D9" t="n">
         <v>136671</v>
@@ -716,19 +908,46 @@
         <v>660</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J9" t="n">
         <v>64345</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>108284</v>
       </c>
-      <c r="J9" t="n">
-        <v>93601.33333333333</v>
+      <c r="L9" t="n">
+        <v>105322</v>
+      </c>
+      <c r="M9" t="n">
+        <v>84139</v>
+      </c>
+      <c r="N9" t="n">
+        <v>92866</v>
+      </c>
+      <c r="O9" t="n">
+        <v>345</v>
+      </c>
+      <c r="P9" t="n">
+        <v>716</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>521.6666666666666</v>
+      </c>
+      <c r="R9" t="n">
+        <v>315</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -739,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="D10" t="n">
         <v>90003</v>
@@ -748,19 +967,46 @@
         <v>610</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="J10" t="n">
         <v>136671</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>79788</v>
       </c>
-      <c r="J10" t="n">
-        <v>97006.33333333333</v>
+      <c r="L10" t="n">
+        <v>114985</v>
+      </c>
+      <c r="M10" t="n">
+        <v>93601.33333333333</v>
+      </c>
+      <c r="N10" t="n">
+        <v>98090.83333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>660</v>
+      </c>
+      <c r="P10" t="n">
+        <v>504</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>503</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -771,7 +1017,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="D11" t="n">
         <v>114184</v>
@@ -780,19 +1026,46 @@
         <v>811</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="G11" t="n">
         <v>4</v>
       </c>
       <c r="H11" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="J11" t="n">
         <v>90003</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>64345</v>
       </c>
-      <c r="J11" t="n">
-        <v>113619.3333333333</v>
+      <c r="L11" t="n">
+        <v>84472</v>
+      </c>
+      <c r="M11" t="n">
+        <v>97006.33333333333</v>
+      </c>
+      <c r="N11" t="n">
+        <v>93927.16666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>610</v>
+      </c>
+      <c r="P11" t="n">
+        <v>345</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>538.3333333333334</v>
+      </c>
+      <c r="R11" t="n">
+        <v>201</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -803,7 +1076,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="n">
         <v>111808</v>
@@ -812,19 +1085,46 @@
         <v>798</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="J12" t="n">
         <v>114184</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>136671</v>
       </c>
-      <c r="J12" t="n">
-        <v>105331.6666666667</v>
+      <c r="L12" t="n">
+        <v>108284</v>
+      </c>
+      <c r="M12" t="n">
+        <v>113619.3333333333</v>
+      </c>
+      <c r="N12" t="n">
+        <v>98879.16666666667</v>
+      </c>
+      <c r="O12" t="n">
+        <v>811</v>
+      </c>
+      <c r="P12" t="n">
+        <v>660</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>693.6666666666666</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-13</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -835,7 +1135,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="D13" t="n">
         <v>92347</v>
@@ -844,19 +1144,46 @@
         <v>648</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
       </c>
       <c r="H13" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
         <v>111808</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>90003</v>
       </c>
-      <c r="J13" t="n">
-        <v>106113</v>
+      <c r="L13" t="n">
+        <v>79788</v>
+      </c>
+      <c r="M13" t="n">
+        <v>105331.6666666667</v>
+      </c>
+      <c r="N13" t="n">
+        <v>99466.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>798</v>
+      </c>
+      <c r="P13" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>739.6666666666666</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-150</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -867,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="D14" t="n">
         <v>102534</v>
@@ -876,19 +1203,46 @@
         <v>770</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J14" t="n">
         <v>92347</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>114184</v>
       </c>
-      <c r="J14" t="n">
-        <v>102229.6666666667</v>
+      <c r="L14" t="n">
+        <v>64345</v>
+      </c>
+      <c r="M14" t="n">
+        <v>106113</v>
+      </c>
+      <c r="N14" t="n">
+        <v>101559.6666666667</v>
+      </c>
+      <c r="O14" t="n">
+        <v>648</v>
+      </c>
+      <c r="P14" t="n">
+        <v>811</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>752.3333333333334</v>
+      </c>
+      <c r="R14" t="n">
+        <v>122</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -899,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="n">
         <v>106254</v>
@@ -908,19 +1262,46 @@
         <v>770</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="J15" t="n">
         <v>102534</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>111808</v>
       </c>
-      <c r="J15" t="n">
-        <v>100378.3333333333</v>
+      <c r="L15" t="n">
+        <v>136671</v>
+      </c>
+      <c r="M15" t="n">
+        <v>102229.6666666667</v>
+      </c>
+      <c r="N15" t="n">
+        <v>107924.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>770</v>
+      </c>
+      <c r="P15" t="n">
+        <v>798</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>738.6666666666666</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -931,7 +1312,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="D16" t="n">
         <v>80544</v>
@@ -940,19 +1321,46 @@
         <v>611</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="J16" t="n">
         <v>106254</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>92347</v>
       </c>
-      <c r="J16" t="n">
-        <v>96444</v>
+      <c r="L16" t="n">
+        <v>90003</v>
+      </c>
+      <c r="M16" t="n">
+        <v>100378.3333333333</v>
+      </c>
+      <c r="N16" t="n">
+        <v>102855</v>
+      </c>
+      <c r="O16" t="n">
+        <v>770</v>
+      </c>
+      <c r="P16" t="n">
+        <v>648</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>729.3333333333334</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-159</v>
+      </c>
+      <c r="S16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -963,7 +1371,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="D17" t="n">
         <v>129836</v>
@@ -972,19 +1380,46 @@
         <v>687</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="J17" t="n">
         <v>80544</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>102534</v>
       </c>
-      <c r="J17" t="n">
-        <v>105544.6666666667</v>
+      <c r="L17" t="n">
+        <v>114184</v>
+      </c>
+      <c r="M17" t="n">
+        <v>96444</v>
+      </c>
+      <c r="N17" t="n">
+        <v>101278.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>611</v>
+      </c>
+      <c r="P17" t="n">
+        <v>770</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>717</v>
+      </c>
+      <c r="R17" t="n">
+        <v>76</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -995,7 +1430,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="D18" t="n">
         <v>113747</v>
@@ -1004,19 +1439,46 @@
         <v>706</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="J18" t="n">
         <v>129836</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>106254</v>
       </c>
-      <c r="J18" t="n">
-        <v>108042.3333333333</v>
+      <c r="L18" t="n">
+        <v>111808</v>
+      </c>
+      <c r="M18" t="n">
+        <v>105544.6666666667</v>
+      </c>
+      <c r="N18" t="n">
+        <v>103887.1666666667</v>
+      </c>
+      <c r="O18" t="n">
+        <v>687</v>
+      </c>
+      <c r="P18" t="n">
+        <v>770</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>689.3333333333334</v>
+      </c>
+      <c r="R18" t="n">
+        <v>19</v>
+      </c>
+      <c r="S18" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1027,7 +1489,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="D19" t="n">
         <v>285837</v>
@@ -1036,19 +1498,46 @@
         <v>645</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J19" t="n">
         <v>113747</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>80544</v>
       </c>
-      <c r="J19" t="n">
-        <v>176473.3333333333</v>
+      <c r="L19" t="n">
+        <v>92347</v>
+      </c>
+      <c r="M19" t="n">
+        <v>108042.3333333333</v>
+      </c>
+      <c r="N19" t="n">
+        <v>104210.3333333333</v>
+      </c>
+      <c r="O19" t="n">
+        <v>706</v>
+      </c>
+      <c r="P19" t="n">
+        <v>611</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>668</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-61</v>
+      </c>
+      <c r="S19" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1059,7 +1548,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="D20" t="n">
         <v>109835</v>
@@ -1068,19 +1557,46 @@
         <v>611</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
       </c>
       <c r="H20" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="J20" t="n">
         <v>285837</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>129836</v>
       </c>
-      <c r="J20" t="n">
-        <v>169806.3333333333</v>
+      <c r="L20" t="n">
+        <v>102534</v>
+      </c>
+      <c r="M20" t="n">
+        <v>176473.3333333333</v>
+      </c>
+      <c r="N20" t="n">
+        <v>136458.6666666667</v>
+      </c>
+      <c r="O20" t="n">
+        <v>645</v>
+      </c>
+      <c r="P20" t="n">
+        <v>687</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>679.3333333333334</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -1091,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="D21" t="n">
         <v>112058</v>
@@ -1100,19 +1616,46 @@
         <v>627</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="G21" t="n">
         <v>3</v>
       </c>
       <c r="H21" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J21" t="n">
         <v>109835</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>113747</v>
       </c>
-      <c r="J21" t="n">
-        <v>169243.3333333333</v>
+      <c r="L21" t="n">
+        <v>106254</v>
+      </c>
+      <c r="M21" t="n">
+        <v>169806.3333333333</v>
+      </c>
+      <c r="N21" t="n">
+        <v>137675.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>611</v>
+      </c>
+      <c r="P21" t="n">
+        <v>706</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>654</v>
+      </c>
+      <c r="R21" t="n">
+        <v>16</v>
+      </c>
+      <c r="S21" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1123,7 +1666,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="D22" t="n">
         <v>99636</v>
@@ -1132,19 +1675,46 @@
         <v>640</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
       </c>
       <c r="H22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="J22" t="n">
         <v>112058</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>285837</v>
       </c>
-      <c r="J22" t="n">
-        <v>107176.3333333333</v>
+      <c r="L22" t="n">
+        <v>80544</v>
+      </c>
+      <c r="M22" t="n">
+        <v>169243.3333333333</v>
+      </c>
+      <c r="N22" t="n">
+        <v>138642.8333333333</v>
+      </c>
+      <c r="O22" t="n">
+        <v>627</v>
+      </c>
+      <c r="P22" t="n">
+        <v>645</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>627.6666666666666</v>
+      </c>
+      <c r="R22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1155,7 +1725,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="D23" t="n">
         <v>146855</v>
@@ -1164,19 +1734,46 @@
         <v>862</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="G23" t="n">
         <v>4</v>
       </c>
       <c r="H23" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="J23" t="n">
         <v>99636</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>109835</v>
       </c>
-      <c r="J23" t="n">
-        <v>119516.3333333333</v>
+      <c r="L23" t="n">
+        <v>129836</v>
+      </c>
+      <c r="M23" t="n">
+        <v>107176.3333333333</v>
+      </c>
+      <c r="N23" t="n">
+        <v>141824.8333333333</v>
+      </c>
+      <c r="O23" t="n">
+        <v>640</v>
+      </c>
+      <c r="P23" t="n">
+        <v>611</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>626</v>
+      </c>
+      <c r="R23" t="n">
+        <v>222</v>
+      </c>
+      <c r="S23" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1187,7 +1784,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="D24" t="n">
         <v>124216</v>
@@ -1196,19 +1793,46 @@
         <v>705</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="G24" t="n">
         <v>4</v>
       </c>
       <c r="H24" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="J24" t="n">
         <v>146855</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>112058</v>
       </c>
-      <c r="J24" t="n">
-        <v>123569</v>
+      <c r="L24" t="n">
+        <v>113747</v>
+      </c>
+      <c r="M24" t="n">
+        <v>119516.3333333333</v>
+      </c>
+      <c r="N24" t="n">
+        <v>144661.3333333333</v>
+      </c>
+      <c r="O24" t="n">
+        <v>862</v>
+      </c>
+      <c r="P24" t="n">
+        <v>627</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>709.6666666666666</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-157</v>
+      </c>
+      <c r="S24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1219,7 +1843,7 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="D25" t="n">
         <v>128306</v>
@@ -1228,19 +1852,46 @@
         <v>718</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="G25" t="n">
         <v>4</v>
       </c>
       <c r="H25" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
         <v>124216</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>99636</v>
       </c>
-      <c r="J25" t="n">
-        <v>133125.6666666667</v>
+      <c r="L25" t="n">
+        <v>285837</v>
+      </c>
+      <c r="M25" t="n">
+        <v>123569</v>
+      </c>
+      <c r="N25" t="n">
+        <v>146406.1666666667</v>
+      </c>
+      <c r="O25" t="n">
+        <v>705</v>
+      </c>
+      <c r="P25" t="n">
+        <v>640</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>735.6666666666666</v>
+      </c>
+      <c r="R25" t="n">
+        <v>13</v>
+      </c>
+      <c r="S25" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1251,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="D26" t="n">
         <v>127741</v>
@@ -1260,19 +1911,46 @@
         <v>834</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J26" t="n">
         <v>128306</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>146855</v>
       </c>
-      <c r="J26" t="n">
-        <v>126754.3333333333</v>
+      <c r="L26" t="n">
+        <v>109835</v>
+      </c>
+      <c r="M26" t="n">
+        <v>133125.6666666667</v>
+      </c>
+      <c r="N26" t="n">
+        <v>120151</v>
+      </c>
+      <c r="O26" t="n">
+        <v>718</v>
+      </c>
+      <c r="P26" t="n">
+        <v>862</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>761.6666666666666</v>
+      </c>
+      <c r="R26" t="n">
+        <v>116</v>
+      </c>
+      <c r="S26" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1283,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="D27" t="n">
         <v>108480</v>
@@ -1292,19 +1970,46 @@
         <v>684</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="J27" t="n">
         <v>127741</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>124216</v>
       </c>
-      <c r="J27" t="n">
-        <v>121509</v>
+      <c r="L27" t="n">
+        <v>112058</v>
+      </c>
+      <c r="M27" t="n">
+        <v>126754.3333333333</v>
+      </c>
+      <c r="N27" t="n">
+        <v>123135.3333333333</v>
+      </c>
+      <c r="O27" t="n">
+        <v>834</v>
+      </c>
+      <c r="P27" t="n">
+        <v>705</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>752.3333333333334</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-150</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1315,7 +2020,7 @@
         <v>3</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="D28" t="n">
         <v>108726</v>
@@ -1324,19 +2029,46 @@
         <v>610</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="J28" t="n">
         <v>108480</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>128306</v>
       </c>
-      <c r="J28" t="n">
-        <v>114982.3333333333</v>
+      <c r="L28" t="n">
+        <v>99636</v>
+      </c>
+      <c r="M28" t="n">
+        <v>121509</v>
+      </c>
+      <c r="N28" t="n">
+        <v>122539</v>
+      </c>
+      <c r="O28" t="n">
+        <v>684</v>
+      </c>
+      <c r="P28" t="n">
+        <v>718</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>745.3333333333334</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-74</v>
+      </c>
+      <c r="S28" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1347,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="D29" t="n">
         <v>117865</v>
@@ -1356,19 +2088,46 @@
         <v>747</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="J29" t="n">
         <v>108726</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>127741</v>
       </c>
-      <c r="J29" t="n">
-        <v>111690.3333333333</v>
+      <c r="L29" t="n">
+        <v>146855</v>
+      </c>
+      <c r="M29" t="n">
+        <v>114982.3333333333</v>
+      </c>
+      <c r="N29" t="n">
+        <v>124054</v>
+      </c>
+      <c r="O29" t="n">
+        <v>610</v>
+      </c>
+      <c r="P29" t="n">
+        <v>834</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>709.3333333333334</v>
+      </c>
+      <c r="R29" t="n">
+        <v>137</v>
+      </c>
+      <c r="S29" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1379,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="D30" t="n">
         <v>112420</v>
@@ -1388,19 +2147,46 @@
         <v>625</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="J30" t="n">
         <v>117865</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>108480</v>
       </c>
-      <c r="J30" t="n">
-        <v>113003.6666666667</v>
+      <c r="L30" t="n">
+        <v>124216</v>
+      </c>
+      <c r="M30" t="n">
+        <v>111690.3333333333</v>
+      </c>
+      <c r="N30" t="n">
+        <v>119222.3333333333</v>
+      </c>
+      <c r="O30" t="n">
+        <v>747</v>
+      </c>
+      <c r="P30" t="n">
+        <v>684</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>680.3333333333334</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-122</v>
+      </c>
+      <c r="S30" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1411,7 +2197,7 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="D31" t="n">
         <v>85067</v>
@@ -1420,19 +2206,46 @@
         <v>471</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J31" t="n">
         <v>112420</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>108726</v>
       </c>
-      <c r="J31" t="n">
-        <v>105117.3333333333</v>
+      <c r="L31" t="n">
+        <v>128306</v>
+      </c>
+      <c r="M31" t="n">
+        <v>113003.6666666667</v>
+      </c>
+      <c r="N31" t="n">
+        <v>117256.3333333333</v>
+      </c>
+      <c r="O31" t="n">
+        <v>625</v>
+      </c>
+      <c r="P31" t="n">
+        <v>610</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>660.6666666666666</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-154</v>
+      </c>
+      <c r="S31" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -1443,7 +2256,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="D32" t="n">
         <v>91171</v>
@@ -1452,19 +2265,46 @@
         <v>513</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
       </c>
       <c r="H32" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="J32" t="n">
         <v>85067</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>117865</v>
       </c>
-      <c r="J32" t="n">
-        <v>96219.33333333333</v>
+      <c r="L32" t="n">
+        <v>127741</v>
+      </c>
+      <c r="M32" t="n">
+        <v>105117.3333333333</v>
+      </c>
+      <c r="N32" t="n">
+        <v>110049.8333333333</v>
+      </c>
+      <c r="O32" t="n">
+        <v>471</v>
+      </c>
+      <c r="P32" t="n">
+        <v>747</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>614.3333333333334</v>
+      </c>
+      <c r="R32" t="n">
+        <v>42</v>
+      </c>
+      <c r="S32" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1475,7 +2315,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="n">
         <v>76700</v>
@@ -1484,19 +2324,46 @@
         <v>471</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="G33" t="n">
         <v>3</v>
       </c>
       <c r="H33" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J33" t="n">
         <v>91171</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>112420</v>
       </c>
-      <c r="J33" t="n">
-        <v>84312.66666666667</v>
+      <c r="L33" t="n">
+        <v>108480</v>
+      </c>
+      <c r="M33" t="n">
+        <v>96219.33333333333</v>
+      </c>
+      <c r="N33" t="n">
+        <v>103954.8333333333</v>
+      </c>
+      <c r="O33" t="n">
+        <v>513</v>
+      </c>
+      <c r="P33" t="n">
+        <v>625</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>536.3333333333334</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-42</v>
+      </c>
+      <c r="S33" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1507,7 +2374,7 @@
         <v>9</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="D34" t="n">
         <v>95680</v>
@@ -1516,19 +2383,46 @@
         <v>638</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="G34" t="n">
         <v>3</v>
       </c>
       <c r="H34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="J34" t="n">
         <v>76700</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>85067</v>
       </c>
-      <c r="J34" t="n">
-        <v>87850.33333333333</v>
+      <c r="L34" t="n">
+        <v>108726</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84312.66666666667</v>
+      </c>
+      <c r="N34" t="n">
+        <v>98658.16666666667</v>
+      </c>
+      <c r="O34" t="n">
+        <v>471</v>
+      </c>
+      <c r="P34" t="n">
+        <v>471</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>485</v>
+      </c>
+      <c r="R34" t="n">
+        <v>167</v>
+      </c>
+      <c r="S34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1539,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="D35" t="n">
         <v>128021</v>
@@ -1548,19 +2442,46 @@
         <v>704</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="G35" t="n">
         <v>4</v>
       </c>
       <c r="H35" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="J35" t="n">
         <v>95680</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>91171</v>
       </c>
-      <c r="J35" t="n">
-        <v>100133.6666666667</v>
+      <c r="L35" t="n">
+        <v>117865</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87850.33333333333</v>
+      </c>
+      <c r="N35" t="n">
+        <v>96483.83333333333</v>
+      </c>
+      <c r="O35" t="n">
+        <v>638</v>
+      </c>
+      <c r="P35" t="n">
+        <v>513</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>540.6666666666666</v>
+      </c>
+      <c r="R35" t="n">
+        <v>66</v>
+      </c>
+      <c r="S35" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -1571,7 +2492,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="D36" t="n">
         <v>95111</v>
@@ -1580,19 +2501,46 @@
         <v>648</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
       </c>
       <c r="H36" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="J36" t="n">
         <v>128021</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>76700</v>
       </c>
-      <c r="J36" t="n">
-        <v>106270.6666666667</v>
+      <c r="L36" t="n">
+        <v>112420</v>
+      </c>
+      <c r="M36" t="n">
+        <v>100133.6666666667</v>
+      </c>
+      <c r="N36" t="n">
+        <v>98176.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>704</v>
+      </c>
+      <c r="P36" t="n">
+        <v>471</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>604.3333333333334</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-56</v>
+      </c>
+      <c r="S36" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -1603,7 +2551,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="D37" t="n">
         <v>106738</v>
@@ -1612,19 +2560,46 @@
         <v>609</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="G37" t="n">
         <v>4</v>
       </c>
       <c r="H37" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
         <v>95111</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>95680</v>
       </c>
-      <c r="J37" t="n">
-        <v>109956.6666666667</v>
+      <c r="L37" t="n">
+        <v>85067</v>
+      </c>
+      <c r="M37" t="n">
+        <v>106270.6666666667</v>
+      </c>
+      <c r="N37" t="n">
+        <v>95291.66666666667</v>
+      </c>
+      <c r="O37" t="n">
+        <v>648</v>
+      </c>
+      <c r="P37" t="n">
+        <v>638</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>663.3333333333334</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-39</v>
+      </c>
+      <c r="S37" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
